--- a/data/controles_results/dif_medias/controls_vars/difmedias_controles_baselines_fixed_2023_T1_2.xlsx
+++ b/data/controles_results/dif_medias/controls_vars/difmedias_controles_baselines_fixed_2023_T1_2.xlsx
@@ -72,58 +72,58 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>5.01e+05</t>
-  </si>
-  <si>
-    <t>(80081.563)</t>
-  </si>
-  <si>
-    <t>490.513</t>
-  </si>
-  <si>
-    <t>(37.593)</t>
-  </si>
-  <si>
-    <t>3.711</t>
+    <t>5.24e+05</t>
+  </si>
+  <si>
+    <t>(80953.804)</t>
+  </si>
+  <si>
+    <t>503.534</t>
+  </si>
+  <si>
+    <t>(38.331)</t>
+  </si>
+  <si>
+    <t>3.714</t>
   </si>
   <si>
     <t>(0.049)</t>
   </si>
   <si>
-    <t>7.179</t>
-  </si>
-  <si>
-    <t>(1.529)</t>
-  </si>
-  <si>
-    <t>87.029</t>
-  </si>
-  <si>
-    <t>(0.515)</t>
-  </si>
-  <si>
-    <t>8.99e+05</t>
-  </si>
-  <si>
-    <t>(55945.145)</t>
-  </si>
-  <si>
-    <t>2.161</t>
+    <t>6.411</t>
+  </si>
+  <si>
+    <t>(1.336)</t>
+  </si>
+  <si>
+    <t>87.003</t>
+  </si>
+  <si>
+    <t>(0.512)</t>
+  </si>
+  <si>
+    <t>8.97e+05</t>
+  </si>
+  <si>
+    <t>(55836.359)</t>
+  </si>
+  <si>
+    <t>2.162</t>
   </si>
   <si>
     <t>(0.135)</t>
   </si>
   <si>
-    <t>2.429</t>
-  </si>
-  <si>
-    <t>(0.416)</t>
-  </si>
-  <si>
-    <t>30.143</t>
-  </si>
-  <si>
-    <t>(4.532)</t>
+    <t>2.339</t>
+  </si>
+  <si>
+    <t>(0.404)</t>
+  </si>
+  <si>
+    <t>29.286</t>
+  </si>
+  <si>
+    <t>(4.490)</t>
   </si>
   <si>
     <t>0.929</t>
@@ -141,58 +141,58 @@
     <t>1</t>
   </si>
   <si>
-    <t>7.19e+05</t>
+    <t>6.98e+05</t>
   </si>
   <si>
     <t>(1.00e+05)</t>
   </si>
   <si>
-    <t>494.616</t>
-  </si>
-  <si>
-    <t>(44.414)</t>
-  </si>
-  <si>
-    <t>3.338</t>
+    <t>482.463</t>
+  </si>
+  <si>
+    <t>(43.823)</t>
+  </si>
+  <si>
+    <t>3.335</t>
   </si>
   <si>
     <t>(0.048)</t>
   </si>
   <si>
-    <t>24.283</t>
-  </si>
-  <si>
-    <t>(3.184)</t>
-  </si>
-  <si>
-    <t>91.486</t>
-  </si>
-  <si>
-    <t>(0.369)</t>
+    <t>25.000</t>
+  </si>
+  <si>
+    <t>(3.191)</t>
+  </si>
+  <si>
+    <t>91.511</t>
+  </si>
+  <si>
+    <t>(0.367)</t>
   </si>
   <si>
     <t>1.38e+06</t>
   </si>
   <si>
-    <t>(57403.269)</t>
-  </si>
-  <si>
-    <t>3.353</t>
+    <t>(57218.217)</t>
+  </si>
+  <si>
+    <t>3.352</t>
   </si>
   <si>
     <t>(0.119)</t>
   </si>
   <si>
-    <t>5.983</t>
-  </si>
-  <si>
-    <t>(0.545)</t>
-  </si>
-  <si>
-    <t>43.400</t>
-  </si>
-  <si>
-    <t>(2.747)</t>
+    <t>6.067</t>
+  </si>
+  <si>
+    <t>(0.544)</t>
+  </si>
+  <si>
+    <t>44.200</t>
+  </si>
+  <si>
+    <t>(2.738)</t>
   </si>
   <si>
     <t>1.000</t>
@@ -216,31 +216,31 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>2.19e+05*</t>
-  </si>
-  <si>
-    <t>4.104</t>
-  </si>
-  <si>
-    <t>-0.374***</t>
-  </si>
-  <si>
-    <t>17.105***</t>
-  </si>
-  <si>
-    <t>4.457***</t>
-  </si>
-  <si>
-    <t>4.78e+05***</t>
-  </si>
-  <si>
-    <t>1.192***</t>
-  </si>
-  <si>
-    <t>3.555***</t>
-  </si>
-  <si>
-    <t>13.257**</t>
+    <t>1.74e+05</t>
+  </si>
+  <si>
+    <t>-21.071</t>
+  </si>
+  <si>
+    <t>-0.380***</t>
+  </si>
+  <si>
+    <t>18.589***</t>
+  </si>
+  <si>
+    <t>4.508***</t>
+  </si>
+  <si>
+    <t>4.82e+05***</t>
+  </si>
+  <si>
+    <t>1.190***</t>
+  </si>
+  <si>
+    <t>3.727***</t>
+  </si>
+  <si>
+    <t>14.914***</t>
   </si>
   <si>
     <t>0.071**</t>

--- a/data/controles_results/dif_medias/controls_vars/difmedias_controles_baselines_fixed_2023_T1_2.xlsx
+++ b/data/controles_results/dif_medias/controls_vars/difmedias_controles_baselines_fixed_2023_T1_2.xlsx
@@ -72,58 +72,58 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>5.24e+05</t>
-  </si>
-  <si>
-    <t>(80953.804)</t>
-  </si>
-  <si>
-    <t>503.534</t>
-  </si>
-  <si>
-    <t>(38.331)</t>
-  </si>
-  <si>
-    <t>3.714</t>
+    <t>5.01e+05</t>
+  </si>
+  <si>
+    <t>(80081.563)</t>
+  </si>
+  <si>
+    <t>490.513</t>
+  </si>
+  <si>
+    <t>(37.593)</t>
+  </si>
+  <si>
+    <t>3.711</t>
   </si>
   <si>
     <t>(0.049)</t>
   </si>
   <si>
-    <t>6.411</t>
-  </si>
-  <si>
-    <t>(1.336)</t>
-  </si>
-  <si>
-    <t>87.003</t>
-  </si>
-  <si>
-    <t>(0.512)</t>
-  </si>
-  <si>
-    <t>8.97e+05</t>
-  </si>
-  <si>
-    <t>(55836.359)</t>
-  </si>
-  <si>
-    <t>2.162</t>
+    <t>7.179</t>
+  </si>
+  <si>
+    <t>(1.529)</t>
+  </si>
+  <si>
+    <t>87.029</t>
+  </si>
+  <si>
+    <t>(0.515)</t>
+  </si>
+  <si>
+    <t>8.99e+05</t>
+  </si>
+  <si>
+    <t>(55945.145)</t>
+  </si>
+  <si>
+    <t>2.161</t>
   </si>
   <si>
     <t>(0.135)</t>
   </si>
   <si>
-    <t>2.339</t>
-  </si>
-  <si>
-    <t>(0.404)</t>
-  </si>
-  <si>
-    <t>29.286</t>
-  </si>
-  <si>
-    <t>(4.490)</t>
+    <t>2.429</t>
+  </si>
+  <si>
+    <t>(0.416)</t>
+  </si>
+  <si>
+    <t>30.143</t>
+  </si>
+  <si>
+    <t>(4.532)</t>
   </si>
   <si>
     <t>0.929</t>
@@ -141,58 +141,58 @@
     <t>1</t>
   </si>
   <si>
-    <t>6.98e+05</t>
+    <t>7.19e+05</t>
   </si>
   <si>
     <t>(1.00e+05)</t>
   </si>
   <si>
-    <t>482.463</t>
-  </si>
-  <si>
-    <t>(43.823)</t>
-  </si>
-  <si>
-    <t>3.335</t>
+    <t>494.616</t>
+  </si>
+  <si>
+    <t>(44.414)</t>
+  </si>
+  <si>
+    <t>3.338</t>
   </si>
   <si>
     <t>(0.048)</t>
   </si>
   <si>
-    <t>25.000</t>
-  </si>
-  <si>
-    <t>(3.191)</t>
-  </si>
-  <si>
-    <t>91.511</t>
-  </si>
-  <si>
-    <t>(0.367)</t>
+    <t>24.283</t>
+  </si>
+  <si>
+    <t>(3.184)</t>
+  </si>
+  <si>
+    <t>91.486</t>
+  </si>
+  <si>
+    <t>(0.369)</t>
   </si>
   <si>
     <t>1.38e+06</t>
   </si>
   <si>
-    <t>(57218.217)</t>
-  </si>
-  <si>
-    <t>3.352</t>
+    <t>(57403.269)</t>
+  </si>
+  <si>
+    <t>3.353</t>
   </si>
   <si>
     <t>(0.119)</t>
   </si>
   <si>
-    <t>6.067</t>
-  </si>
-  <si>
-    <t>(0.544)</t>
-  </si>
-  <si>
-    <t>44.200</t>
-  </si>
-  <si>
-    <t>(2.738)</t>
+    <t>5.983</t>
+  </si>
+  <si>
+    <t>(0.545)</t>
+  </si>
+  <si>
+    <t>43.400</t>
+  </si>
+  <si>
+    <t>(2.747)</t>
   </si>
   <si>
     <t>1.000</t>
@@ -216,31 +216,31 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>1.74e+05</t>
-  </si>
-  <si>
-    <t>-21.071</t>
-  </si>
-  <si>
-    <t>-0.380***</t>
-  </si>
-  <si>
-    <t>18.589***</t>
-  </si>
-  <si>
-    <t>4.508***</t>
-  </si>
-  <si>
-    <t>4.82e+05***</t>
-  </si>
-  <si>
-    <t>1.190***</t>
-  </si>
-  <si>
-    <t>3.727***</t>
-  </si>
-  <si>
-    <t>14.914***</t>
+    <t>2.19e+05*</t>
+  </si>
+  <si>
+    <t>4.104</t>
+  </si>
+  <si>
+    <t>-0.374***</t>
+  </si>
+  <si>
+    <t>17.105***</t>
+  </si>
+  <si>
+    <t>4.457***</t>
+  </si>
+  <si>
+    <t>4.78e+05***</t>
+  </si>
+  <si>
+    <t>1.192***</t>
+  </si>
+  <si>
+    <t>3.555***</t>
+  </si>
+  <si>
+    <t>13.257**</t>
   </si>
   <si>
     <t>0.071**</t>
